--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -16152,14 +16152,14 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
         <v>15651000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>26172</v>
+        <v>26216</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>15651000</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>26172</v>
+        <v>26216</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -68956,10 +68956,10 @@
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>H | 598呎 (3房)
+          <t>H | 597呎 (3房)
 $1565万
-$26,172/呎
-(26年-07月-17日)</t>
+$26,216/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -56204,7 +56204,7 @@
       </c>
       <c r="G897" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H897" s="5" t="n">
@@ -74927,7 +74927,7 @@
           <t>E | 452呎 (2房)
 $999万
 $22,097/呎
-(26年-07月-27日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -53529,7 +53529,7 @@
         </is>
       </c>
       <c r="E854" s="4" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F854" s="3" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>8772000</v>
       </c>
       <c r="I854" s="5" t="n">
-        <v>25207</v>
+        <v>25135</v>
       </c>
       <c r="J854" s="3" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>8772000</v>
       </c>
       <c r="L854" s="5" t="n">
-        <v>25207</v>
+        <v>25135</v>
       </c>
       <c r="M854" s="3" t="inlineStr">
         <is>
@@ -74600,9 +74600,9 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>H | 348呎 (1房)
+          <t>H | 349呎 (1房)
 $877万
-$25,207/呎
+$25,135/呎
 (22年-05月-17日)</t>
         </is>
       </c>

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>11784000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>26541</v>
+        <v>26600</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>11784000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>26541</v>
+        <v>26600</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -67213,9 +67213,9 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 444呎 (2房)
+          <t>B | 443呎 (2房)
 $1178万
-$26,541/呎
+$26,600/呎
 (21年-07月-23日)</t>
         </is>
       </c>
